--- a/truc.xlsx
+++ b/truc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANHAN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\bvdkthoilai-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{683734A5-32C8-446F-8E59-014AD5DFAD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDCB4C4-7D00-4414-A0D0-422AE8F971FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8B4F0781-E3A5-4069-9398-E5B358392BAB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="182">
   <si>
     <t>BS. CKI  LÊ THÀNH NHƠN</t>
   </si>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t>BỆNH VIỆN</t>
-  </si>
-  <si>
-    <t>SỐ ĐIỆN THOẠIz</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -262,21 +259,6 @@
     <t>Nội – Nhi – ĐY</t>
   </si>
   <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <t>Điều Dưỡng, HSTH, KTV</t>
-  </si>
-  <si>
-    <t>Bác Sĩ</t>
-  </si>
-  <si>
-    <t>KHOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>Thiện</t>
   </si>
   <si>
@@ -584,6 +566,21 @@
   </si>
   <si>
     <t>SỞ Y TẾ TP CẦN THƠ</t>
+  </si>
+  <si>
+    <t>Thường trực lãnh đạo</t>
+  </si>
+  <si>
+    <t>BSCKSII. Trần Quốc Luận(Thường Trực 24/7, SĐT:0943068189)</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>ANIT</t>
+  </si>
+  <si>
+    <t>SỐ ĐIỆN THOẠI</t>
   </si>
 </sst>
 </file>
@@ -819,52 +816,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -876,46 +837,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -925,7 +846,92 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1348,1104 +1354,1118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="38" t="s">
+      <c r="A1" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="28"/>
+      <c r="C10" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="28"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="28"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="28"/>
+      <c r="B14" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="28"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="28"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="28"/>
+      <c r="C18" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="P20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="28"/>
+      <c r="C21" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="28"/>
+      <c r="C22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="28"/>
+      <c r="C24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="28"/>
+      <c r="C27" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="28"/>
+      <c r="C42" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="28"/>
+      <c r="C44" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+    </row>
+    <row r="49" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="37"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-    </row>
-    <row r="6" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="J19" s="20"/>
-      <c r="P19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="8"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="8"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="8"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="8"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="8"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="8"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="8"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="8"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="8"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="8"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="8"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="8"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="8"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="8"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="8"/>
-    </row>
-    <row r="48" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-    </row>
-    <row r="49" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4" t="s">
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="I49" s="4"/>
+      <c r="I49" s="28"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="3" t="s">
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="6" t="s">
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="6"/>
+      <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="3" t="s">
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="6" t="s">
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="I51" s="6"/>
+      <c r="I51" s="41"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="3">
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="2">
         <v>2923.6814880000002</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4">
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28">
         <v>2923.7350759999999</v>
       </c>
-      <c r="I52" s="4"/>
+      <c r="I52" s="28"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="3" t="s">
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4">
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28">
         <v>2923.8607390000002</v>
       </c>
-      <c r="I53" s="4"/>
+      <c r="I53" s="28"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="3" t="s">
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="3" t="s">
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="1" t="s">
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="3" t="s">
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="3">
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="2">
         <v>2923.689711</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="3">
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="2">
         <v>2923.6810019999998</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="3">
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="2">
         <v>2923.6891449999998</v>
       </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="1" t="s">
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="101">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="H51:I51"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A57:C57"/>
@@ -2457,16 +2477,8 @@
     <mergeCell ref="H53:I53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="E52:G52"/>
     <mergeCell ref="H52:I52"/>
@@ -2482,16 +2494,15 @@
     <mergeCell ref="C46:H46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="C47:H47"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="A30:B30"/>
@@ -2506,32 +2517,42 @@
     <mergeCell ref="C34:H34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="C35:H35"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:H39"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:I9"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:C8"/>
@@ -2542,12 +2563,6 @@
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.43307086614173229" top="0.23622047244094491" bottom="0.23622047244094491" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>
   <pageSetup paperSize="9" scale="80" fitToWidth="0" orientation="portrait" r:id="rId1"/>
